--- a/samples/fixtures/xlsx/sov.xlsx
+++ b/samples/fixtures/xlsx/sov.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,16 @@
           <t>Sprinklered</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>YearBuilt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +457,14 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -461,6 +479,152 @@
         <is>
           <t>yes</t>
         </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7 Dockside</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9 Pier End</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha Wharf</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beta Dock</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gamma Yard</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Delta Port</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2018</v>
       </c>
     </row>
   </sheetData>
